--- a/output/pdf_financials_xlsx/NVLH.xlsx
+++ b/output/pdf_financials_xlsx/NVLH.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="24">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="28">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="30">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.698097</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.515469</v>
       </c>
     </row>
     <row r="93">
@@ -2580,7 +2580,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>5.698097</v>
       </c>
@@ -4300,10 +4304,10 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2.395149</v>
+        <v>-2.395149</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>2.282999</v>
+        <v>-2.282999</v>
       </c>
     </row>
     <row r="79">
@@ -4352,10 +4356,10 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2.404846</v>
+        <v>-2.404846</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>2.265773</v>
+        <v>-2.265773</v>
       </c>
     </row>
     <row r="81">

--- a/output/pdf_financials_xlsx/NVLH.xlsx
+++ b/output/pdf_financials_xlsx/NVLH.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.190042</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.087078</v>
       </c>
     </row>
     <row r="13">
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.395149</v>
+        <v>-2.205107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.282999</v>
+        <v>-2.195921</v>
       </c>
     </row>
     <row r="28">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.395149</v>
+        <v>-2.205107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.282999</v>
+        <v>-2.195921</v>
       </c>
     </row>
     <row r="30">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
